--- a/election_results_1970.xlsx
+++ b/election_results_1970.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\Dropbox\UK_GE\New_UK_Map\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\Dropbox\UK_GE\UK_Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC285F77-A84C-4246-885F-D8CD05B260C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA49F1F-F96E-4A71-9B8D-7E311D7963F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
